--- a/uploads/schools.xlsx
+++ b/uploads/schools.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Llewellyn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Llewellyn\Desktop\py\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118C1645-1253-4426-A55D-DB90B2836FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F015B1-FFEC-44A5-98BE-797EE7921776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="165">
   <si>
     <t>EMIS</t>
   </si>
@@ -557,6 +557,9 @@
   </si>
   <si>
     <t>yes 02/06/2025</t>
+  </si>
+  <si>
+    <t>Volop Intermediate School</t>
   </si>
 </sst>
 </file>
@@ -657,7 +660,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -706,11 +709,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -760,6 +774,9 @@
     </xf>
     <xf numFmtId="1" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1073,7 +1090,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:X86"/>
+  <dimension ref="A1:X87"/>
   <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="16"/>
@@ -7288,6 +7305,32 @@
         <v>115</v>
       </c>
     </row>
+    <row r="87" spans="1:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="18">
+        <v>300043215</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="18">
+        <v>5</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G87" s="18">
+        <v>3</v>
+      </c>
+      <c r="H87" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="S87">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:X86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B2:B44">
@@ -7296,7 +7339,7 @@
   <conditionalFormatting sqref="B45">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B86">
+  <conditionalFormatting sqref="B45:B87">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.51181102362204722" right="0.11811023622047245" top="0.35433070866141736" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
